--- a/excel/MultiAnalytesMU.xlsx
+++ b/excel/MultiAnalytesMU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tim\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_C6A45A312DA437D555892B102EC6DC653C84F05D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37A231A0-923D-4E2D-8E47-F43797F9275D}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_C6A45A312DA437D555892B102EC6DC653C84F05D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04BDD6CC-DD2E-4DC6-916F-6220FB7C85A5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="38" windowWidth="15960" windowHeight="18083" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="38" windowWidth="15960" windowHeight="18083" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MainTable" sheetId="1" r:id="rId1"/>
@@ -1424,7 +1424,7 @@
     <t>This spread-sheet is "Public Domain". Anyone is free to copy, modify, publish, use, or distribute it for any purpose, commercial or non-commercial, and by any means. The author is retired; carries out "Pro Bono" work only; and does not accept any responsibility for any loss caused by the use of, or failure to use, this spreadsheet.   Please do not remove my name, copyright &amp; version information.</t>
   </si>
   <si>
-    <t xml:space="preserve">Version: 2023-06-010   -   ©Tim Strutt. </t>
+    <t xml:space="preserve">Version: 2026-06-02   -   ©Tim Strutt. </t>
   </si>
 </sst>
 </file>
@@ -3035,78 +3035,6 @@
     <xf numFmtId="49" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3131,20 +3059,92 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3648,7 +3648,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{C572A759-6A51-4108-AA02-DFA0A04FC94B}">
-            <ma14:wrappingTextBoxFlag xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:ma14="http://schemas.microsoft.com/office/mac/drawingml/2011/main" val="1"/>
+            <ma14:wrappingTextBoxFlag xmlns:ma14="http://schemas.microsoft.com/office/mac/drawingml/2011/main" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" val="1"/>
           </a:ext>
         </a:extLst>
       </xdr:spPr>
@@ -4200,7 +4200,7 @@
         <a:effectLst/>
         <a:extLst>
           <a:ext uri="{C572A759-6A51-4108-AA02-DFA0A04FC94B}">
-            <ma14:wrappingTextBoxFlag xmlns="" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:ma14="http://schemas.microsoft.com/office/mac/drawingml/2011/main" val="1"/>
+            <ma14:wrappingTextBoxFlag xmlns:ma14="http://schemas.microsoft.com/office/mac/drawingml/2011/main" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="" val="1"/>
           </a:ext>
         </a:extLst>
       </xdr:spPr>
@@ -5352,10 +5352,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:27" ht="20.65" customHeight="1">
-      <c r="B1" s="139" t="s">
+      <c r="B1" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="140"/>
+      <c r="C1" s="169"/>
       <c r="D1" s="2" t="str">
         <f>IF(ISTEXT(SampleResults!$A$1),SampleResults!$A$1,"TestName")</f>
         <v>ICP-MS</v>
@@ -5454,10 +5454,10 @@
       </c>
     </row>
     <row r="2" spans="2:27" ht="20.65" customHeight="1">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="142"/>
+      <c r="C2" s="171"/>
       <c r="D2" s="3" t="str">
         <f>SampleResults!B1</f>
         <v>Al</v>
@@ -5556,114 +5556,114 @@
       </c>
     </row>
     <row r="3" spans="2:27" ht="14.25" customHeight="1">
-      <c r="B3" s="163" t="s">
+      <c r="B3" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="164" t="s">
+      <c r="C3" s="140" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="4" t="str">
         <f t="shared" ref="D3:AA3" si="1">C3</f>
         <v>Low Spike</v>
       </c>
-      <c r="E3" s="165" t="str">
+      <c r="E3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="F3" s="165" t="str">
+      <c r="F3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="G3" s="165" t="str">
+      <c r="G3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="H3" s="165" t="str">
+      <c r="H3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="I3" s="165" t="str">
+      <c r="I3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="J3" s="165" t="str">
+      <c r="J3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="K3" s="165" t="str">
+      <c r="K3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="L3" s="165" t="str">
+      <c r="L3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="M3" s="165" t="str">
+      <c r="M3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="N3" s="165" t="str">
+      <c r="N3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="O3" s="165" t="str">
+      <c r="O3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="P3" s="165" t="str">
+      <c r="P3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="Q3" s="165" t="str">
+      <c r="Q3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="R3" s="165" t="str">
+      <c r="R3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="S3" s="165" t="str">
+      <c r="S3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="T3" s="165" t="str">
+      <c r="T3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="U3" s="165" t="str">
+      <c r="U3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="V3" s="165" t="str">
+      <c r="V3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="W3" s="165" t="str">
+      <c r="W3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="X3" s="165" t="str">
+      <c r="X3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="Y3" s="165" t="str">
+      <c r="Y3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="Z3" s="165" t="str">
+      <c r="Z3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
-      <c r="AA3" s="165" t="str">
+      <c r="AA3" s="141" t="str">
         <f t="shared" si="1"/>
         <v>Low Spike</v>
       </c>
     </row>
     <row r="4" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B4" s="166" t="s">
+      <c r="B4" s="142" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="167" t="s">
+      <c r="C4" s="143" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="5" t="str">
@@ -5764,10 +5764,10 @@
       </c>
     </row>
     <row r="5" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B5" s="168" t="s">
+      <c r="B5" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="169">
+      <c r="C5" s="145">
         <v>2</v>
       </c>
       <c r="D5" s="7">
@@ -5868,10 +5868,10 @@
       </c>
     </row>
     <row r="6" spans="2:27" s="113" customFormat="1" ht="18" customHeight="1">
-      <c r="B6" s="147" t="s">
+      <c r="B6" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="148"/>
+      <c r="C6" s="154"/>
       <c r="D6" s="125">
         <v>90</v>
       </c>
@@ -5946,10 +5946,10 @@
       </c>
     </row>
     <row r="7" spans="2:27" s="113" customFormat="1" ht="18" customHeight="1">
-      <c r="B7" s="149" t="s">
+      <c r="B7" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="150"/>
+      <c r="C7" s="156"/>
       <c r="D7" s="126"/>
       <c r="E7" s="126"/>
       <c r="F7" s="126"/>
@@ -5978,10 +5978,10 @@
       <c r="AA7" s="126"/>
     </row>
     <row r="8" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B8" s="158" t="s">
+      <c r="B8" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="153"/>
+      <c r="C8" s="160"/>
       <c r="D8" s="8">
         <f t="shared" ref="D8:AA8" si="4">IF(D38&gt;0,D25+D38&amp;" ("&amp;D38&amp;" Excluded!)",D25)</f>
         <v>9</v>
@@ -6080,10 +6080,10 @@
       </c>
     </row>
     <row r="9" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B9" s="159" t="s">
+      <c r="B9" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="155"/>
+      <c r="C9" s="162"/>
       <c r="D9" s="10">
         <f t="shared" ref="D9:AA9" si="5">IF(D25&gt;0,D27/D26,0)</f>
         <v>0.12465678855305257</v>
@@ -6182,10 +6182,10 @@
       </c>
     </row>
     <row r="10" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B10" s="160" t="s">
+      <c r="B10" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="157"/>
+      <c r="C10" s="152"/>
       <c r="D10" s="11">
         <f t="shared" ref="D10:AA10" si="6">IFERROR(IF(D3="Blank",0,(1-D16)),0)</f>
         <v>0.10579012345679017</v>
@@ -6284,217 +6284,217 @@
       </c>
     </row>
     <row r="11" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B11" s="170" t="str">
+      <c r="B11" s="167" t="str">
         <f>"Horwitz Ratio (Ideally 0.3≤HorRat≤1) "&amp;IF(COUNTIFS(D11:AA11,"&gt;2")," Check: Very High",IF(COUNTIFS(D11:AA11,"&gt;1"),"Check: High",IF(COUNTIFS(D11:AA11,"&lt;0.3"),"Check: Low?","- OK")))</f>
         <v>Horwitz Ratio (Ideally 0.3≤HorRat≤1)  Check: Very High</v>
       </c>
-      <c r="C11" s="153"/>
-      <c r="D11" s="171">
+      <c r="C11" s="160"/>
+      <c r="D11" s="146">
         <f>((D9*100)/D30)</f>
         <v>0.56662176615023896</v>
       </c>
-      <c r="E11" s="171">
+      <c r="E11" s="146">
         <f t="shared" ref="E11:AA11" si="7">((E9*100)/E30)</f>
         <v>0.39809262390051747</v>
       </c>
-      <c r="F11" s="171">
+      <c r="F11" s="146">
         <f t="shared" si="7"/>
         <v>0.18964907421821264</v>
       </c>
-      <c r="G11" s="171">
+      <c r="G11" s="146">
         <f t="shared" si="7"/>
         <v>0.74006368409650802</v>
       </c>
-      <c r="H11" s="171">
+      <c r="H11" s="146">
         <f t="shared" si="7"/>
         <v>6.5323728942165706</v>
       </c>
-      <c r="I11" s="171">
+      <c r="I11" s="146">
         <f t="shared" si="7"/>
         <v>0.31395513340596604</v>
       </c>
-      <c r="J11" s="171">
+      <c r="J11" s="146">
         <f t="shared" si="7"/>
         <v>0.32211169364731773</v>
       </c>
-      <c r="K11" s="171">
+      <c r="K11" s="146">
         <f t="shared" si="7"/>
         <v>0.65263742504388056</v>
       </c>
-      <c r="L11" s="171">
+      <c r="L11" s="146">
         <f t="shared" si="7"/>
         <v>0.33772810122343117</v>
       </c>
-      <c r="M11" s="171">
+      <c r="M11" s="146">
         <f t="shared" si="7"/>
         <v>0.30528504343259777</v>
       </c>
-      <c r="N11" s="171">
+      <c r="N11" s="146">
         <f t="shared" si="7"/>
         <v>0.33679336319786224</v>
       </c>
-      <c r="O11" s="171">
+      <c r="O11" s="146">
         <f t="shared" si="7"/>
         <v>0.4430652405970037</v>
       </c>
-      <c r="P11" s="171">
+      <c r="P11" s="146">
         <f t="shared" si="7"/>
         <v>0.31352188711202661</v>
       </c>
-      <c r="Q11" s="171">
+      <c r="Q11" s="146">
         <f t="shared" si="7"/>
         <v>0.32938051707510696</v>
       </c>
-      <c r="R11" s="171">
+      <c r="R11" s="146">
         <f t="shared" si="7"/>
         <v>0.50919907984552271</v>
       </c>
-      <c r="S11" s="171">
+      <c r="S11" s="146">
         <f t="shared" si="7"/>
         <v>0.45919921755381482</v>
       </c>
-      <c r="T11" s="171">
+      <c r="T11" s="146">
         <f t="shared" si="7"/>
         <v>0.32724766983123993</v>
       </c>
-      <c r="U11" s="171">
+      <c r="U11" s="146">
         <f t="shared" si="7"/>
         <v>0.35553918756826353</v>
       </c>
-      <c r="V11" s="171">
+      <c r="V11" s="146">
         <f t="shared" si="7"/>
         <v>0.49353355987867326</v>
       </c>
-      <c r="W11" s="171">
+      <c r="W11" s="146">
         <f t="shared" si="7"/>
         <v>0.43084670520478485</v>
       </c>
-      <c r="X11" s="171">
+      <c r="X11" s="146">
         <f t="shared" si="7"/>
         <v>0.49614755851640718</v>
       </c>
-      <c r="Y11" s="171">
+      <c r="Y11" s="146">
         <f t="shared" si="7"/>
         <v>0.49614755851640385</v>
       </c>
-      <c r="Z11" s="171">
+      <c r="Z11" s="146">
         <f t="shared" si="7"/>
         <v>0.49790901355794515</v>
       </c>
-      <c r="AA11" s="171">
+      <c r="AA11" s="146">
         <f t="shared" si="7"/>
         <v>0.30863235406215456</v>
       </c>
     </row>
     <row r="12" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B12" s="172" t="str">
+      <c r="B12" s="151" t="str">
         <f>IF(COUNTIFS(D12:AA12,"&gt;0")," Grubbs' Outlier Check : "&amp;COUNTIFS(D12:AA12,"&gt;0")&amp;" Found?"," Grubbs' Outlier Check")</f>
         <v xml:space="preserve"> Grubbs' Outlier Check : 4 Found?</v>
       </c>
-      <c r="C12" s="157"/>
-      <c r="D12" s="173">
+      <c r="C12" s="152"/>
+      <c r="D12" s="147">
         <f t="shared" ref="D12:AA12" si="8">IFERROR(IF(D34&lt;D36,IF(D35&lt;D36,0,D19),D20),0)</f>
         <v>58.97</v>
       </c>
-      <c r="E12" s="173">
+      <c r="E12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F12" s="173">
+      <c r="F12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G12" s="173">
+      <c r="G12" s="147">
         <f t="shared" si="8"/>
         <v>140.1</v>
       </c>
-      <c r="H12" s="173">
+      <c r="H12" s="147">
         <f t="shared" si="8"/>
         <v>771</v>
       </c>
-      <c r="I12" s="173">
+      <c r="I12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J12" s="173">
+      <c r="J12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K12" s="173">
+      <c r="K12" s="147">
         <f t="shared" si="8"/>
         <v>53.77</v>
       </c>
-      <c r="L12" s="173">
+      <c r="L12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M12" s="173">
+      <c r="M12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N12" s="173">
+      <c r="N12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="O12" s="173">
+      <c r="O12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="P12" s="173">
+      <c r="P12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="173">
+      <c r="Q12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R12" s="173">
+      <c r="R12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S12" s="173">
+      <c r="S12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T12" s="173">
+      <c r="T12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U12" s="173">
+      <c r="U12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V12" s="173">
+      <c r="V12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W12" s="173">
+      <c r="W12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X12" s="173">
+      <c r="X12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Y12" s="173">
+      <c r="Y12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="173">
+      <c r="Z12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="173">
+      <c r="AA12" s="147">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B13" s="152" t="str">
+      <c r="B13" s="159" t="str">
         <f>" Result to "&amp;D5&amp;" Significant figures"</f>
         <v xml:space="preserve"> Result to 2 Significant figures</v>
       </c>
-      <c r="C13" s="153"/>
+      <c r="C13" s="160"/>
       <c r="D13" s="12" t="str">
         <f t="shared" ref="D13:AA13" si="9">IFERROR(FIXED(D26,((-1*INT(LOG10(D26)))-1)+D5,TRUE),0)</f>
         <v>80</v>
@@ -6593,10 +6593,10 @@
       </c>
     </row>
     <row r="14" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B14" s="154" t="s">
+      <c r="B14" s="161" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="155"/>
+      <c r="C14" s="162"/>
       <c r="D14" s="13" t="str">
         <f t="shared" ref="D14:AA14" si="10">IFERROR(IF(D3="Blank",0,D51),0)</f>
         <v>32</v>
@@ -6695,10 +6695,10 @@
       </c>
     </row>
     <row r="15" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B15" s="154" t="s">
+      <c r="B15" s="161" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="155"/>
+      <c r="C15" s="162"/>
       <c r="D15" s="13" t="str">
         <f t="shared" ref="D15:AA15" si="11">IFERROR(IF(D3="Blank",0,D45),0)</f>
         <v>97</v>
@@ -6797,10 +6797,10 @@
       </c>
     </row>
     <row r="16" spans="2:27" ht="16.899999999999999" customHeight="1">
-      <c r="B16" s="156" t="s">
+      <c r="B16" s="163" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="157"/>
+      <c r="C16" s="152"/>
       <c r="D16" s="14">
         <f t="shared" ref="D16:AA16" si="12">IFERROR(IF(D3="Blank","Blank",(D26)/D6),0)</f>
         <v>0.89420987654320983</v>
@@ -6899,8 +6899,8 @@
       </c>
     </row>
     <row r="17" spans="2:27" ht="16.899999999999999" hidden="1" customHeight="1">
-      <c r="B17" s="143"/>
-      <c r="C17" s="144"/>
+      <c r="B17" s="172"/>
+      <c r="C17" s="150"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="15"/>
@@ -7235,8 +7235,8 @@
       </c>
     </row>
     <row r="21" spans="2:27" ht="16.899999999999999" hidden="1" customHeight="1">
-      <c r="B21" s="145"/>
-      <c r="C21" s="144"/>
+      <c r="B21" s="158"/>
+      <c r="C21" s="150"/>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
       <c r="F21" s="19"/>
@@ -7263,8 +7263,8 @@
       <c r="AA21" s="19"/>
     </row>
     <row r="22" spans="2:27" ht="16.899999999999999" hidden="1" customHeight="1">
-      <c r="B22" s="145"/>
-      <c r="C22" s="144"/>
+      <c r="B22" s="158"/>
+      <c r="C22" s="150"/>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
       <c r="F22" s="19"/>
@@ -7291,8 +7291,8 @@
       <c r="AA22" s="19"/>
     </row>
     <row r="23" spans="2:27" ht="16.899999999999999" hidden="1" customHeight="1">
-      <c r="B23" s="145"/>
-      <c r="C23" s="144"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="150"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
@@ -7319,10 +7319,10 @@
       <c r="AA23" s="19"/>
     </row>
     <row r="24" spans="2:27" ht="16.899999999999999" hidden="1" customHeight="1">
-      <c r="B24" s="151" t="s">
+      <c r="B24" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="144"/>
+      <c r="C24" s="150"/>
       <c r="D24" s="20" t="str">
         <f t="shared" ref="D24:AA24" si="14">IFERROR(IF(D3="Blank","Blank",D46),0)</f>
         <v>90</v>
@@ -8645,7 +8645,7 @@
       </c>
     </row>
     <row r="37" spans="2:27" ht="16.899999999999999" hidden="1" customHeight="1">
-      <c r="B37" s="174"/>
+      <c r="B37" s="148"/>
       <c r="C37" s="136"/>
       <c r="D37" s="30"/>
       <c r="E37" s="30"/>
@@ -10057,10 +10057,10 @@
       <c r="AA52" s="42"/>
     </row>
     <row r="53" spans="2:27" s="129" customFormat="1" ht="16.899999999999999" customHeight="1">
-      <c r="B53" s="146" t="s">
+      <c r="B53" s="149" t="s">
         <v>43</v>
       </c>
-      <c r="C53" s="144"/>
+      <c r="C53" s="150"/>
       <c r="D53" s="128" t="str">
         <f t="shared" ref="D53:AA53" si="33">IF(ISTEXT(D7),"MDL not a Number!",IFERROR(IF(D3="Blank","Blank: "&amp;D51&amp;" "&amp;IF(D7&gt;0,"^"&amp;D4,D4),IF(D7&gt;D6,"MDL &gt; Spike!",IF(D7&gt;0,D46&amp;" ± "&amp;D51&amp;" ^"&amp;D4,D46&amp;" ± "&amp;D51&amp;" "&amp;D4))),"Error!!"))</f>
         <v>90 ± 32 µg/kg</v>
@@ -10159,7 +10159,13 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B6:C6"/>
@@ -10174,11 +10180,6 @@
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <conditionalFormatting sqref="C5">
     <cfRule type="cellIs" dxfId="33" priority="6" stopIfTrue="1" operator="notEqual">
@@ -10321,7 +10322,7 @@
       <formula1>"Spike,Blank,Low Spike,Reference Material"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"ppm,ppb,ppt,mg/kg,µg/kg,ng/kg,mg/L,µg/L,ng/L,pg/L,g/L,drops/floz"</formula1>
+      <formula1>"ppm,ppb,ppt,mg/kg,µg/kg,ng/kg,mg/L,µg/L,ng/L,pg/L,g/L,percent,drops/floz"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"2,1,3"</formula1>
@@ -11785,10 +11786,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="161" t="s">
+      <c r="A1" s="173" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="162"/>
+      <c r="B1" s="174"/>
       <c r="C1" s="45" t="s">
         <v>79</v>
       </c>
@@ -12797,7 +12798,7 @@
       <c r="F12" s="103"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7gZhxIrQeaHx8Hk3qKuvGwFLnzIbREY8xAc117tx1fAGQ17U7ftNNJmASnfOoNQ4ySAmtrE0iQ8qE23dbyoW+A==" saltValue="vT2y5TfEi2AJpf9tls49tw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="1.1436999999999999" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="77" orientation="portrait"/>
   <headerFooter>
